--- a/education_forms/049_mba_program_giveaway_entry--education_forms.xlsx
+++ b/education_forms/049_mba_program_giveaway_entry--education_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -694,12 +694,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>motivation</t>
+          <t>motivation_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Motivation</t>
+          <t>Motivation 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,7 +722,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Motivation</t>
+          <t>Motivation2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,7 +745,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Motivation</t>
+          <t>Motivation3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,7 +768,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Motivation</t>
+          <t>Motivation4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,7 +791,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Motivation</t>
+          <t>Motivation5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,7 +814,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Motivation</t>
+          <t>Motivation6</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,7 +837,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Motivation</t>
+          <t>Motivation7</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,7 +860,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Motivation</t>
+          <t>Motivation8</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,7 +883,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Motivation</t>
+          <t>Motivation9</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,7 +906,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Motivation</t>
+          <t>Motivation10</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
